--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -75,25 +75,7 @@
     <t xml:space="preserve">备注</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">置信度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(%)</t>
-    </r>
+    <t xml:space="preserve">置信度(%)</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-21</t>
@@ -133,6 +115,590 @@
   </si>
   <si>
     <t xml:space="preserve">周一06:30定时执行失败(UTC时钟周日误判)，10:15手动补跑；基准价为10:15实时价(晚于06:00切点)；口径已改为当日趋势</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25 06:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12.66%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">站上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三个月新高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线上方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持仓回升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(COMEX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">538t)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">霍尔木兹避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">航运</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-90%)+9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月降息押注升温；风险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后获利回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元指数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上方偏强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">杰克逊霍尔年会前观望</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；档位押中不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能放缓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元偏强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年会前观望</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -440,72 +1006,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间生成预测时，把报告中方向置信度同步记入本列；用于校准分析（各置信度档的声称把握 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际命中率），攒够 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个已结算样本后运行 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">scripts/calibration.py </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出校准报告</t>
-    </r>
+    <t xml:space="preserve">晨间生成预测时，把报告中方向置信度同步记入本列；用于校准分析（各置信度档的声称把握 vs 实际命中率），攒够 20 个已结算样本后运行 scripts/calibration.py 出校准报告</t>
   </si>
 </sst>
 </file>
@@ -555,13 +1056,13 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -703,7 +1204,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -715,7 +1216,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -731,7 +1232,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -739,11 +1240,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -767,10 +1272,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -779,7 +1280,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,7 +1498,7 @@
       <c r="Q2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1026,26 +1527,28 @@
       <c r="H3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="11" t="str">
+      <c r="I3" s="9" t="n">
+        <v>4659</v>
+      </c>
+      <c r="J3" s="11" t="n">
         <f aca="false">IF(OR(I3="",C3=""),"",(I3-C3)/C3)</f>
-        <v/>
+        <v>0.00325157733801339</v>
       </c>
       <c r="K3" s="8" t="str">
         <f aca="false">IF(J3="","",IF(J3&gt;0,"涨",IF(J3&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L3" s="8" t="str">
         <f aca="false">IF(J3="","",IF(ABS(J3)&lt;=0.003,"小",IF(ABS(J3)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M3" s="8" t="str">
         <f aca="false">IF(OR(D3="",K3=""),"",IF(D3=K3,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N3" s="8" t="str">
         <f aca="false">IF(OR(E3="",L3=""),"",IF(E3=L3,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>28</v>
@@ -1056,19 +1559,35 @@
       <c r="Q3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>4659</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="7" t="str">
         <f aca="false">IF(OR(I4="",C4=""),"",(I4-C4)/C4)</f>
@@ -1090,9 +1609,18 @@
         <f aca="false">IF(OR(E4="",L4=""),"",IF(E4=L4,"√","×"))</f>
         <v/>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="O4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8"/>
@@ -14616,111 +15144,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>31</v>
+      <c r="A1" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="A5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="17" t="n">
+      <c r="A6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="14" t="str">
+      <c r="A10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>41</v>
+      <c r="A12" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -14748,47 +15276,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14796,7 +15324,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14804,39 +15332,39 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>64</v>
+      <c r="B13" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -126,6 +126,21 @@
     <t xml:space="preserve">中</t>
   </si>
   <si>
+    <t xml:space="preserve">动能延续(站上$4600三个月新高,200日线上方)+央行购金(PBOC 6月+15t连买20月)+持仓回升(COMEX净多6月+16%至538t)+霍尔木兹避险(航运-90%)+9月降息押注升温；风险:连涨5.6%后获利回吐/美元指数101上方偏强/VIX回落15.1/杰克逊霍尔年会前观望</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周二06:30定时执行成功(克隆仓库版)；档位押中不押大:昨日仅+0.33%动能放缓+美元偏强+年会前观望</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26 06:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -162,7 +177,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+12.66%)</t>
+      <t xml:space="preserve">+14.45%)</t>
     </r>
   </si>
   <si>
@@ -173,7 +188,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动能延续</t>
+      <t xml:space="preserve">动能衰减</t>
     </r>
     <r>
       <rPr>
@@ -183,7 +198,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">(+0.33%→+0.19%)+PCE</t>
     </r>
     <r>
       <rPr>
@@ -192,7 +207,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">站上</t>
+      <t xml:space="preserve">公布前观望；趋势结构完好</t>
     </r>
     <r>
       <rPr>
@@ -202,7 +217,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">$4600</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -211,7 +226,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三个月新高</t>
+      <t xml:space="preserve">日</t>
     </r>
     <r>
       <rPr>
@@ -221,7 +236,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">,200</t>
+      <t xml:space="preserve">+14.45%,200</t>
     </r>
     <r>
       <rPr>
@@ -240,45 +255,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行购金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(PBOC 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15t</t>
+      <t xml:space="preserve">)+PBOC</t>
     </r>
     <r>
       <rPr>
@@ -316,7 +293,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -325,121 +302,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">持仓回升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(COMEX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">净多</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+16%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">538t)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">霍尔木兹避险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">航运</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-90%)+9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月降息押注升温；风险</t>
+      <t xml:space="preserve">霍尔木兹避险垫底；风险</t>
     </r>
     <r>
       <rPr>
@@ -458,7 +321,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连涨</t>
+      <t xml:space="preserve">今晚</t>
     </r>
     <r>
       <rPr>
@@ -468,7 +331,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5.6%</t>
+      <t xml:space="preserve">PCE</t>
     </r>
     <r>
       <rPr>
@@ -477,83 +340,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">后获利回吐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元指数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">101</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上方偏强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回落</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15.1/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">杰克逊霍尔年会前观望</t>
+      <t xml:space="preserve">偏热或冲高回落</t>
     </r>
   </si>
   <si>
@@ -564,7 +351,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周二</t>
+      <t xml:space="preserve">周三</t>
     </r>
     <r>
       <rPr>
@@ -574,7 +361,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:30</t>
+      <t xml:space="preserve">06:31</t>
     </r>
     <r>
       <rPr>
@@ -621,7 +408,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；档位押中不押大</t>
+      <t xml:space="preserve">；档位改押小</t>
     </r>
     <r>
       <rPr>
@@ -640,7 +427,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昨日仅</t>
+      <t xml:space="preserve">动能连续衰减</t>
     </r>
     <r>
       <rPr>
@@ -650,7 +437,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.33%</t>
+      <t xml:space="preserve">+PCE</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +446,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动能放缓</t>
+      <t xml:space="preserve">前观望</t>
     </r>
     <r>
       <rPr>
@@ -669,7 +456,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+</t>
+      <t xml:space="preserve">+VIX15.85</t>
     </r>
     <r>
       <rPr>
@@ -678,26 +465,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美元偏强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年会前观望</t>
+      <t xml:space="preserve">低位</t>
     </r>
   </si>
   <si>
@@ -1240,7 +1008,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1573,64 +1341,82 @@
       <c r="C4" s="5" t="n">
         <v>4659</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="7" t="str">
+      <c r="I4" s="5" t="n">
+        <v>4667.8</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <f aca="false">IF(OR(I4="",C4=""),"",(I4-C4)/C4)</f>
-        <v/>
+        <v>0.00188881734277746</v>
       </c>
       <c r="K4" s="4" t="str">
         <f aca="false">IF(J4="","",IF(J4&gt;0,"涨",IF(J4&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L4" s="4" t="str">
         <f aca="false">IF(J4="","",IF(ABS(J4)&lt;=0.003,"小",IF(ABS(J4)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M4" s="4" t="str">
         <f aca="false">IF(OR(D4="",K4=""),"",IF(D4=K4,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N4" s="4" t="str">
         <f aca="false">IF(OR(E4="",L4=""),"",IF(E4=L4,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O4" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="1" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>4667.8</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I5" s="9"/>
       <c r="J5" s="11" t="str">
         <f aca="false">IF(OR(I5="",C5=""),"",(I5-C5)/C5)</f>
@@ -1652,9 +1438,18 @@
         <f aca="false">IF(OR(E5="",L5=""),"",IF(E5=L5,"√","×"))</f>
         <v/>
       </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
+      <c r="O5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
@@ -15145,30 +14940,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
@@ -15177,16 +14972,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.5</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
@@ -15195,16 +14990,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.5</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
@@ -15213,7 +15008,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -15222,33 +15017,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -15276,47 +15071,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15324,7 +15119,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15332,31 +15127,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15364,7 +15159,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="82">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -141,6 +141,24 @@
     <t xml:space="preserve">小</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势涨(20日+14.45%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">动能衰减(+0.33%→+0.19%)+PCE公布前观望；趋势结构完好(20日+14.45%,200日线上方)+PBOC连买20月+霍尔木兹避险垫底；风险:今晚PCE偏热或冲高回落</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周三06:31定时执行成功(克隆仓库版)；档位改押小:动能连续衰减+PCE前观望+VIX15.85低位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27 06:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">跌</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -177,7 +195,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+14.45%)</t>
+      <t xml:space="preserve">+14.75%)</t>
     </r>
   </si>
   <si>
@@ -185,10 +203,20 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动能衰减</t>
+      <t xml:space="preserve">偏热鹰派重定价</t>
     </r>
     <r>
       <rPr>
@@ -198,7 +226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(+0.33%→+0.19%)+PCE</t>
+      <t xml:space="preserve">(9</t>
     </r>
     <r>
       <rPr>
@@ -207,7 +235,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">公布前观望；趋势结构完好</t>
+      <t xml:space="preserve">月</t>
     </r>
     <r>
       <rPr>
@@ -217,7 +245,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(20</t>
+      <t xml:space="preserve">hold</t>
     </r>
     <r>
       <rPr>
@@ -226,7 +254,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">概率</t>
     </r>
     <r>
       <rPr>
@@ -236,7 +264,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+14.45%,200</t>
+      <t xml:space="preserve">68%→60%,</t>
     </r>
     <r>
       <rPr>
@@ -245,7 +273,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日线上方</t>
+      <t xml:space="preserve">加息押注</t>
     </r>
     <r>
       <rPr>
@@ -255,7 +283,102 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+PBOC</t>
+      <t xml:space="preserve">40%)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元走强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双顶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4664/4668</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两度受阻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能三连衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+1.78%→-1.04%→-1.20%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC</t>
     </r>
     <r>
       <rPr>
@@ -293,6 +416,63 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">,6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+14.9t)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">委内瑞拉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伊朗地缘避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">+</t>
     </r>
     <r>
@@ -302,7 +482,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">霍尔木兹避险垫底；风险</t>
+      <t xml:space="preserve">昨夜</t>
     </r>
     <r>
       <rPr>
@@ -312,7 +492,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">:</t>
+      <t xml:space="preserve">4594</t>
     </r>
     <r>
       <rPr>
@@ -321,26 +501,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">今晚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热或冲高回落</t>
+      <t xml:space="preserve">低点快速承接垫底；杰克逊霍尔年会开幕前波动收敛</t>
     </r>
   </si>
   <si>
@@ -351,7 +512,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周三</t>
+      <t xml:space="preserve">周四</t>
     </r>
     <r>
       <rPr>
@@ -361,7 +522,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:31</t>
+      <t xml:space="preserve">06:32</t>
     </r>
     <r>
       <rPr>
@@ -408,7 +569,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；档位改押小</t>
+      <t xml:space="preserve">；方向押跌</t>
     </r>
     <r>
       <rPr>
@@ -418,7 +579,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">:</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -427,7 +588,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动能连续衰减</t>
+      <t xml:space="preserve">档位押小</t>
     </r>
     <r>
       <rPr>
@@ -437,7 +598,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+PCE</t>
+      <t xml:space="preserve">:PCE</t>
     </r>
     <r>
       <rPr>
@@ -446,7 +607,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">前观望</t>
+      <t xml:space="preserve">偏热余波</t>
     </r>
     <r>
       <rPr>
@@ -456,7 +617,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+VIX15.85</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -465,7 +626,74 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">低位</t>
+      <t xml:space="preserve">鹰派重定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年会前观望；基于当日信号独立判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">防追结果式反向修正</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日双错</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -1008,7 +1236,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1402,64 +1630,82 @@
       <c r="C5" s="9" t="n">
         <v>4667.8</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="11" t="str">
+      <c r="I5" s="9" t="n">
+        <v>4611.8</v>
+      </c>
+      <c r="J5" s="11" t="n">
         <f aca="false">IF(OR(I5="",C5=""),"",(I5-C5)/C5)</f>
-        <v/>
+        <v>-0.011997086421869</v>
       </c>
       <c r="K5" s="8" t="str">
         <f aca="false">IF(J5="","",IF(J5&gt;0,"涨",IF(J5&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L5" s="8" t="str">
         <f aca="false">IF(J5="","",IF(ABS(J5)&lt;=0.003,"小",IF(ABS(J5)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M5" s="8" t="str">
         <f aca="false">IF(OR(D5="",K5=""),"",IF(D5=K5,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N5" s="8" t="str">
         <f aca="false">IF(OR(E5="",L5=""),"",IF(E5=L5,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O5" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4611.5</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="7" t="str">
         <f aca="false">IF(OR(I6="",C6=""),"",(I6-C6)/C6)</f>
@@ -1481,9 +1727,18 @@
         <f aca="false">IF(OR(E6="",L6=""),"",IF(E6=L6,"√","×"))</f>
         <v/>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="O6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8"/>
@@ -14940,75 +15195,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -15017,33 +15272,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -15071,47 +15326,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15119,7 +15374,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15127,31 +15382,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15159,7 +15414,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -159,44 +159,7 @@
     <t xml:space="preserve">跌</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+14.75%)</t>
-    </r>
+    <t xml:space="preserve">趋势涨(20日+14.75%)</t>
   </si>
   <si>
     <r>
@@ -505,196 +468,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；方向押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押小</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热余波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派重定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年会前观望；基于当日信号独立判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">防追结果式反向修正</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日双错</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">周四06:32定时执行成功(克隆仓库版)；方向押跌+档位押小:PCE偏热余波+鹰派重定价+年会前观望；基于当日信号独立判断,防追结果式反向修正(昨日双错)</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1004,6 +778,846 @@
   <si>
     <t xml:space="preserve">晨间生成预测时，把报告中方向置信度同步记入本列；用于校准分析（各置信度档的声称把握 vs 实际命中率），攒够 20 个已结算样本后运行 scripts/calibration.py 出校准报告</t>
   </si>
+  <si>
+    <t xml:space="preserve">短期超买指标</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个交易日累计涨幅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">标记</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买区域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。超买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重大事件前夜三重叠加→方向从</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下调至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先验提升；超买但无事件→档位额外下调一档。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增设，复盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向预测错误（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前夜，方向本应押跌）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">流动性冲击信号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单日飙升超</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金价同步下跌→标记</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">流动性冲击模式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，档位额外上调一档；全球主要股指连跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+→"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">流动性冲击预警</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，方向偏空先验提升。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增设</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">市况分层标签</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">市况标签拆为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期趋势</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日动能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，两者背离时报告提示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期看多但短期调整</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增设</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">信号定价度</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">报告信号分解每条标注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]/[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]/[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，区分已被市场消化的利好与尚未释放的利空。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增设</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">场景树</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">报告人工审核区含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条条件路径（触发条件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结果档位），供人工审核快速定位。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增设</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1236,10 +1850,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1282,6 +1892,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1691,19 +2305,19 @@
       <c r="C6" s="5" t="n">
         <v>4611.5</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="5"/>
@@ -1727,16 +2341,16 @@
         <f aca="false">IF(OR(E6="",L6=""),"",IF(E6=L6,"√","×"))</f>
         <v/>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="6" t="s">
         <v>45</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -15194,84 +15808,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="14" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="16" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="15" t="str">
+      <c r="B10" s="14" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>57</v>
       </c>
     </row>
@@ -15317,7 +15931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -15325,87 +15939,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>80</v>
       </c>
     </row>
@@ -15415,6 +16029,46 @@
       </c>
       <c r="B13" s="3" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="97">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -471,6 +471,768 @@
     <t xml:space="preserve">周四06:32定时执行成功(克隆仓库版)；方向押跌+档位押小:PCE偏热余波+鹰派重定价+年会前观望；基于当日信号独立判断,防追结果式反向修正(昨日双错)</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28 06:38</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15.76%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派重定价延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息押注升至约四成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元偏强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通胀粘性推升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DXY)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术面转弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日均线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,MACD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">负值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,RSI45)+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15.76%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买获利盘；托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:4594-4596</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支撑两度承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+19.9t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月以来最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">委内瑞拉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伊朗地缘避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+CFTC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净多回升；今晚沃什年会讲话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前波动收敛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派重定价余波</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术面弱势</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买回调</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">但跌幅收敛企稳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.20%→-0.05%)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支撑有力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沃什讲话前观望→押小档；基于当日信号独立判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式跟风</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日双对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">黄金预测评分统计</t>
   </si>
   <si>
@@ -782,300 +1544,7 @@
     <t xml:space="preserve">短期超买指标</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个交易日累计涨幅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt;8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标记</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超买区域</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。超买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重大事件前夜三重叠加→方向从</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下调至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">先验提升；超买但无事件→档位额外下调一档。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增设，复盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8/26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向预测错误（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.75%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前夜，方向本应押跌）</t>
-    </r>
+    <t xml:space="preserve">近20个交易日累计涨幅&gt;8%标记"超买区域"。超买+动能衰减+重大事件前夜三重叠加→方向从"涨"下调至"跌"先验提升；超买但无事件→档位额外下调一档。2026-08-27增设，复盘8/26方向预测错误（20日涨14.75%超买+PCE前夜，方向本应押跌）</t>
   </si>
   <si>
     <t xml:space="preserve">流动性冲击信号</t>
@@ -1257,366 +1726,19 @@
     <t xml:space="preserve">市况分层标签</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">市况标签拆为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期趋势</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日动能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，两者背离时报告提示</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期看多但短期调整</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增设</t>
-    </r>
+    <t xml:space="preserve">市况标签拆为"长期趋势(60日方向)+短期状态(10日动能)"，两者背离时报告提示"长期看多但短期调整"。2026-08-27增设</t>
   </si>
   <si>
     <t xml:space="preserve">信号定价度</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">报告信号分解每条标注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]/[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]/[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，区分已被市场消化的利好与尚未释放的利空。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增设</t>
-    </r>
+    <t xml:space="preserve">报告信号分解每条标注[已定价]/[部分定价]/[未释放]，区分已被市场消化的利好与尚未释放的利空。2026-08-27增设</t>
   </si>
   <si>
     <t xml:space="preserve">场景树</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">报告人工审核区含</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条条件路径（触发条件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结果档位），供人工审核快速定位。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-08-27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增设</t>
-    </r>
+    <t xml:space="preserve">报告人工审核区含2-3条条件路径（触发条件+概率+结果档位），供人工审核快速定位。2026-08-27增设</t>
   </si>
 </sst>
 </file>
@@ -1850,6 +1972,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1892,10 +2018,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2320,26 +2442,28 @@
       <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="7" t="str">
+      <c r="I6" s="5" t="n">
+        <v>4609.2</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <f aca="false">IF(OR(I6="",C6=""),"",(I6-C6)/C6)</f>
-        <v/>
+        <v>-0.000498753117207022</v>
       </c>
       <c r="K6" s="4" t="str">
         <f aca="false">IF(J6="","",IF(J6&gt;0,"涨",IF(J6&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L6" s="4" t="str">
         <f aca="false">IF(J6="","",IF(ABS(J6)&lt;=0.003,"小",IF(ABS(J6)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M6" s="4" t="str">
         <f aca="false">IF(OR(D6="",K6=""),"",IF(D6=K6,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N6" s="4" t="str">
         <f aca="false">IF(OR(E6="",L6=""),"",IF(E6=L6,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>45</v>
@@ -2355,14 +2479,30 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>4608.8</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I7" s="9"/>
       <c r="J7" s="11" t="str">
         <f aca="false">IF(OR(I7="",C7=""),"",(I7-C7)/C7)</f>
@@ -2384,9 +2524,18 @@
         <f aca="false">IF(OR(E7="",L7=""),"",IF(E7=L7,"√","×"))</f>
         <v/>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
+      <c r="O7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
@@ -15808,111 +15957,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>48</v>
+      <c r="A1" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="A5" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="17" t="n">
+      <c r="A6" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="14" t="str">
+      <c r="A10" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>57</v>
+      <c r="A12" s="19" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -15939,88 +16088,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>62</v>
+      <c r="A1" s="20" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>64</v>
+      <c r="A3" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>66</v>
+      <c r="A4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>68</v>
+      <c r="A5" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>70</v>
+      <c r="A6" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>72</v>
+      <c r="A7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>73</v>
+      <c r="B8" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>74</v>
+      <c r="B9" s="22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>76</v>
+      <c r="A10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>78</v>
+      <c r="A11" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>80</v>
+      <c r="A12" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16028,47 +16177,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="23" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -477,760 +477,13 @@
     <t xml:space="preserve">2026-08-28 06:38</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15.76%)</t>
-    </r>
+    <t xml:space="preserve">趋势涨(20日+15.76%)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派重定价延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息押注升至约四成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元偏强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通胀粘性推升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DXY)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术面转弱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日均线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,MACD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">负值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,RSI45)+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15.76%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超买获利盘；托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:4594-4596</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支撑两度承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+19.9t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,2023</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月以来最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">委内瑞拉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伊朗地缘避险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+CFTC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">净多回升；今晚沃什年会讲话</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22:00)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前波动收敛</t>
-    </r>
+    <t xml:space="preserve">鹰派重定价延续(偏热PCE后9月加息押注升至约四成)+美元偏强(通胀粘性推升DXY)+技术面转弱(跌破5日/50日均线,MACD负值,RSI45)+20日+15.76%超买获利盘；托底:4594-4596支撑两度承接+PBOC连买21月(7月+19.9t加速,2023年10月以来最大)+委内瑞拉/伊朗地缘避险+CFTC净多回升；今晚沃什年会讲话(约22:00)前波动收敛</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:38</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；方向押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押小</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派重定价余波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术面弱势</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超买回调</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">但跌幅收敛企稳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-1.20%→-0.05%)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支撑有力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">沃什讲话前观望→押小档；基于当日信号独立判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式跟风</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日双对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">周五06:38定时执行成功(克隆仓库版)；方向押跌+档位押小:鹰派重定价余波+技术面弱势+超买回调,但跌幅收敛企稳(-1.20%→-0.05%)+支撑有力+沃什讲话前观望→押小档；基于当日信号独立判断,非追结果式跟风(昨日双对)</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1923,7 +1176,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1969,10 +1222,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2488,52 +1737,54 @@
       <c r="C7" s="9" t="n">
         <v>4608.8</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="11" t="str">
+      <c r="I7" s="9" t="n">
+        <v>4456.4</v>
+      </c>
+      <c r="J7" s="11" t="n">
         <f aca="false">IF(OR(I7="",C7=""),"",(I7-C7)/C7)</f>
-        <v/>
+        <v>-0.0330671758375283</v>
       </c>
       <c r="K7" s="8" t="str">
         <f aca="false">IF(J7="","",IF(J7&gt;0,"涨",IF(J7&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L7" s="8" t="str">
         <f aca="false">IF(J7="","",IF(ABS(J7)&lt;=0.003,"小",IF(ABS(J7)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M7" s="8" t="str">
         <f aca="false">IF(OR(D7="",K7=""),"",IF(D7=K7,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N7" s="8" t="str">
         <f aca="false">IF(OR(E7="",L7=""),"",IF(E7=L7,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O7" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -15957,84 +15208,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="14" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.8</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="16" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.8</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.8</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="15" t="str">
+      <c r="B10" s="14" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>62</v>
       </c>
     </row>
@@ -16053,7 +15304,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16088,87 +15339,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>85</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="102">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -484,6 +484,587 @@
   </si>
   <si>
     <t xml:space="preserve">周五06:38定时执行成功(克隆仓库版)；方向押跌+档位押小:鹰派重定价余波+技术面弱势+超买回调,但跌幅收敛企稳(-1.20%→-0.05%)+支撑有力+沃什讲话前观望→押小档；基于当日信号独立判断,非追结果式跟风(昨日双对)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31 06:38</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+13.32%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">沃什杰克逊霍尔放鹰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加息定价升至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50%+)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元美债收益率走强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术破位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/4515-4527</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">汇合区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三只乌鸦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+13.32%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买获利盘；托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+19.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+4441-4367</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">缺口承接区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地缘尾部</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五暴跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后惯性下探</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4441→4425</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">缺口区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">急跌次日波幅收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行逢低买盘限制深跌→押中档；昨日档位押小被大档打脸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">累计档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2/6),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断基于当日信号独立作出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式上修</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1176,7 +1757,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1222,6 +1803,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1789,14 +2374,30 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4459.5</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="7" t="str">
         <f aca="false">IF(OR(I8="",C8=""),"",(I8-C8)/C8)</f>
@@ -1818,9 +2419,18 @@
         <f aca="false">IF(OR(E8="",L8=""),"",IF(E8=L8,"√","×"))</f>
         <v/>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="O8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8"/>
@@ -15208,99 +15818,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>53</v>
+      <c r="A1" s="13" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="A5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.833333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="17" t="n">
+      <c r="A6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.833333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.833333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="14" t="str">
+      <c r="A10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>62</v>
+      <c r="A12" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -15309,10 +15919,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -15339,88 +15949,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>67</v>
+      <c r="A1" s="20" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>69</v>
+      <c r="A3" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>71</v>
+      <c r="A4" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>73</v>
+      <c r="A5" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>75</v>
+      <c r="A6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>77</v>
+      <c r="A7" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>78</v>
+      <c r="B8" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>79</v>
+      <c r="B9" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>81</v>
+      <c r="A10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>83</v>
+      <c r="A11" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>85</v>
+      <c r="A12" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15428,47 +16038,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -492,6 +492,21 @@
     <t xml:space="preserve">2026-08-31 06:38</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势涨(20日+13.32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沃什杰克逊霍尔放鹰(2026加息定价升至50%+)+美元美债收益率走强+技术破位(跌破200日线/4515-4527汇合区,三只乌鸦)+20日+13.32%超买获利盘；托底:PBOC连买21月(7月+19.9吨)+4441-4367缺口承接区+地缘尾部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周一06:45定时执行成功(克隆仓库版)；方向押跌+档位押中:周五暴跌-3.3%后惯性下探4441→4425缺口区,急跌次日波幅收敛+央行逢低买盘限制深跌→押中档；昨日档位押小被大档打脸(累计档位2/6),本判断基于当日信号独立作出,非追结果式上修</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01 07:08</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -539,7 +554,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">沃什杰克逊霍尔放鹰</t>
+      <t xml:space="preserve">鹰派主线未逆转</t>
     </r>
     <r>
       <rPr>
@@ -558,7 +573,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">加息定价升至</t>
+      <t xml:space="preserve">加息定价</t>
     </r>
     <r>
       <rPr>
@@ -568,7 +583,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">50%+)+</t>
+      <t xml:space="preserve">50%+</t>
     </r>
     <r>
       <rPr>
@@ -577,7 +592,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美元美债收益率走强</t>
+      <t xml:space="preserve">美元偏强</t>
     </r>
     <r>
       <rPr>
@@ -587,7 +602,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+</t>
+      <t xml:space="preserve">)+</t>
     </r>
     <r>
       <rPr>
@@ -596,7 +611,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">技术破位</t>
+      <t xml:space="preserve">技术压制</t>
     </r>
     <r>
       <rPr>
@@ -606,26 +621,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200</t>
+      <t xml:space="preserve">(200</t>
     </r>
     <r>
       <rPr>
@@ -644,7 +640,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/4515-4527</t>
+      <t xml:space="preserve">4529</t>
     </r>
     <r>
       <rPr>
@@ -653,7 +649,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">汇合区</t>
+      <t xml:space="preserve">下方</t>
     </r>
     <r>
       <rPr>
@@ -663,7 +659,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">,</t>
+      <t xml:space="preserve">,MACD</t>
     </r>
     <r>
       <rPr>
@@ -672,7 +668,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三只乌鸦</t>
+      <t xml:space="preserve">负值区</t>
     </r>
     <r>
       <rPr>
@@ -682,7 +678,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+20</t>
+      <t xml:space="preserve">)→</t>
     </r>
     <r>
       <rPr>
@@ -691,7 +687,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">惯性偏弱；托底</t>
     </r>
     <r>
       <rPr>
@@ -701,7 +697,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+13.32%</t>
+      <t xml:space="preserve">:4441</t>
     </r>
     <r>
       <rPr>
@@ -710,7 +706,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">超买获利盘；托底</t>
+      <t xml:space="preserve">承接昨日午后实战验证</t>
     </r>
     <r>
       <rPr>
@@ -720,7 +716,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">:PBOC</t>
+      <t xml:space="preserve">(4444</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">被拉回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+PBOC</t>
     </r>
     <r>
       <rPr>
@@ -796,7 +811,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+4441-4367</t>
+      <t xml:space="preserve">)+</t>
     </r>
     <r>
       <rPr>
@@ -805,7 +820,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">缺口承接区</t>
+      <t xml:space="preserve">地缘尾部；空头动能急剧衰竭</t>
     </r>
     <r>
       <rPr>
@@ -815,7 +830,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+</t>
+      <t xml:space="preserve">(-3.31%→-0.19%)</t>
     </r>
     <r>
       <rPr>
@@ -824,7 +839,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">地缘尾部</t>
+      <t xml:space="preserve">但缺反弹催化→低位窄幅整理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押小档</t>
     </r>
   </si>
   <si>
@@ -835,7 +869,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周一</t>
+      <t xml:space="preserve">周二</t>
     </r>
     <r>
       <rPr>
@@ -845,7 +879,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:45</t>
+      <t xml:space="preserve">07:06</t>
     </r>
     <r>
       <rPr>
@@ -854,7 +888,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">定时执行成功</t>
+      <t xml:space="preserve">晨间定时执行成功</t>
     </r>
     <r>
       <rPr>
@@ -911,7 +945,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位押中</t>
+      <t xml:space="preserve">档位押小</t>
     </r>
     <r>
       <rPr>
@@ -930,7 +964,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周五暴跌</t>
+      <t xml:space="preserve">急跌后动能衰竭</t>
     </r>
     <r>
       <rPr>
@@ -940,7 +974,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-3.3%</t>
+      <t xml:space="preserve">(-3.3%→-0.19%)+4441</t>
     </r>
     <r>
       <rPr>
@@ -949,45 +983,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">后惯性下探</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4441→4425</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">缺口区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">急跌次日波幅收敛</t>
+      <t xml:space="preserve">承接实战验证</t>
     </r>
     <r>
       <rPr>
@@ -1006,7 +1002,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">央行逢低买盘限制深跌→押中档；昨日档位押小被大档打脸</t>
+      <t xml:space="preserve">日内区间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4441-4473</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宽度仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.7%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主线鹰派未逆转但无反弹催化；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押中被小档打脸</t>
     </r>
     <r>
       <rPr>
@@ -1025,7 +1078,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">累计档位</t>
+      <t xml:space="preserve">累计方向</t>
     </r>
     <r>
       <rPr>
@@ -1035,7 +1088,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2/6),</t>
+      <t xml:space="preserve">6/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2/7),</t>
     </r>
     <r>
       <rPr>
@@ -1063,7 +1135,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非追结果式上修</t>
+      <t xml:space="preserve">非追结果式下修</t>
     </r>
   </si>
   <si>
@@ -1806,7 +1878,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2383,64 +2455,82 @@
       <c r="C8" s="5" t="n">
         <v>4459.5</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="7" t="str">
+      <c r="I8" s="5" t="n">
+        <v>4450.9</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <f aca="false">IF(OR(I8="",C8=""),"",(I8-C8)/C8)</f>
-        <v/>
+        <v>-0.00192846731696387</v>
       </c>
       <c r="K8" s="4" t="str">
         <f aca="false">IF(J8="","",IF(J8&gt;0,"涨",IF(J8&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L8" s="4" t="str">
         <f aca="false">IF(J8="","",IF(ABS(J8)&lt;=0.003,"小",IF(ABS(J8)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M8" s="4" t="str">
         <f aca="false">IF(OR(D8="",K8=""),"",IF(D8=K8,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N8" s="4" t="str">
         <f aca="false">IF(OR(E8="",L8=""),"",IF(E8=L8,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O8" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>4451.7</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I9" s="9"/>
       <c r="J9" s="11" t="str">
         <f aca="false">IF(OR(I9="",C9=""),"",(I9-C9)/C9)</f>
@@ -2462,9 +2552,18 @@
         <f aca="false">IF(OR(E9="",L9=""),"",IF(E9=L9,"√","×"))</f>
         <v/>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
+      <c r="O9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
@@ -15819,75 +15918,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.833333333333333</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.833333333333333</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.833333333333333</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -15896,33 +15995,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -15950,47 +16049,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15998,7 +16097,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16006,31 +16105,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16038,47 +16137,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -507,361 +507,18 @@
     <t xml:space="preserve">2026-09-01 07:08</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+13.32%)</t>
-    </r>
+    <t xml:space="preserve">鹰派主线未逆转(2026加息定价50%+美元偏强)+技术压制(200日线4529下方,MACD负值区)→惯性偏弱；托底:4441承接昨日午后实战验证(4444被拉回)+PBOC连买21月(7月+19.9吨)+地缘尾部；空头动能急剧衰竭(-3.31%→-0.19%)但缺反弹催化→低位窄幅整理,押小档</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派主线未逆转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加息定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元偏强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术压制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4529</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,MACD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">负值区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">惯性偏弱；托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:4441</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">承接昨日午后实战验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4444</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">被拉回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+19.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">地缘尾部；空头动能急剧衰竭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-3.31%→-0.19%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">但缺反弹催化→低位窄幅整理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押小档</t>
-    </r>
+    <t xml:space="preserve">周二07:06晨间定时执行成功(克隆仓库版)；方向押跌+档位押小:急跌后动能衰竭(-3.3%→-0.19%)+4441承接实战验证+日内区间4441-4473宽度仅0.7%,主线鹰派未逆转但无反弹催化；8/31押中被小档打脸(累计方向6/7、档位2/7),本判断基于当日信号独立作出,非追结果式下修</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02 06:40</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -869,7 +526,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周二</t>
+      <t xml:space="preserve">趋势涨转急跌</t>
     </r>
     <r>
       <rPr>
@@ -879,7 +536,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">07:06</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -888,6 +545,494 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">日现货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已退出超买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.0%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派主线未逆转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月维持利率概率约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54%+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加息押注近半</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术破位深化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4370/4346,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收于全天低位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">惯性偏空；托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:4313-4335</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重支撑汇合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月平台</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回撤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月突破位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吨近三年最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买解除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日现货口径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.9%&lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阈值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+VIX14.92</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无流动性冲击；连跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后首测厚支撑→押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">晨间定时执行成功</t>
     </r>
     <r>
@@ -945,7 +1090,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位押小</t>
+      <t xml:space="preserve">档位押中</t>
     </r>
     <r>
       <rPr>
@@ -964,7 +1109,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">急跌后动能衰竭</t>
+      <t xml:space="preserve">鹰派主线</t>
     </r>
     <r>
       <rPr>
@@ -974,7 +1119,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(-3.3%→-0.19%)+4441</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -983,7 +1128,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">承接实战验证</t>
+      <t xml:space="preserve">破位惯性</t>
     </r>
     <r>
       <rPr>
@@ -1002,7 +1147,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日内区间</t>
+      <t xml:space="preserve">跌速急升</t>
     </r>
     <r>
       <rPr>
@@ -1012,7 +1157,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4441-4473</t>
+      <t xml:space="preserve">(-0.19%→-2.75%),</t>
     </r>
     <r>
       <rPr>
@@ -1021,7 +1166,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">宽度仅</t>
+      <t xml:space="preserve">但</t>
     </r>
     <r>
       <rPr>
@@ -1031,7 +1176,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.7%,</t>
+      <t xml:space="preserve">4313-4335</t>
     </r>
     <r>
       <rPr>
@@ -1040,7 +1185,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">主线鹰派未逆转但无反弹催化；</t>
+      <t xml:space="preserve">三重支撑首测</t>
     </r>
     <r>
       <rPr>
@@ -1050,7 +1195,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8/31</t>
+      <t xml:space="preserve">+PBOC</t>
     </r>
     <r>
       <rPr>
@@ -1059,7 +1204,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">押中被小档打脸</t>
+      <t xml:space="preserve">逢低加速</t>
     </r>
     <r>
       <rPr>
@@ -1069,6 +1214,25 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超买已解除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
@@ -1078,6 +1242,120 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">现货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.9%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">限制深跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小档区间几何宽度仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.36%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">难命中→押中档；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押小被大档打脸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">累计方向</t>
     </r>
     <r>
@@ -1088,7 +1366,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6/7</t>
+      <t xml:space="preserve">7/8</t>
     </r>
     <r>
       <rPr>
@@ -1107,7 +1385,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2/7),</t>
+      <t xml:space="preserve">2/8),</t>
     </r>
     <r>
       <rPr>
@@ -1135,7 +1413,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非追结果式下修</t>
+      <t xml:space="preserve">非追结果式上修</t>
     </r>
   </si>
   <si>
@@ -1878,7 +2156,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2516,64 +2794,82 @@
       <c r="C9" s="9" t="n">
         <v>4451.7</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="11" t="str">
+      <c r="I9" s="9" t="n">
+        <v>4329.1</v>
+      </c>
+      <c r="J9" s="11" t="n">
         <f aca="false">IF(OR(I9="",C9=""),"",(I9-C9)/C9)</f>
-        <v/>
+        <v>-0.027540040883258</v>
       </c>
       <c r="K9" s="8" t="str">
         <f aca="false">IF(J9="","",IF(J9&gt;0,"涨",IF(J9&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L9" s="8" t="str">
         <f aca="false">IF(J9="","",IF(ABS(J9)&lt;=0.003,"小",IF(ABS(J9)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M9" s="8" t="str">
         <f aca="false">IF(OR(D9="",K9=""),"",IF(D9=K9,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N9" s="8" t="str">
         <f aca="false">IF(OR(E9="",L9=""),"",IF(E9=L9,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O9" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="Q9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Q9" s="12" t="s">
+      <c r="R9" s="1" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="R9" s="0" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>4329.1</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="7" t="str">
         <f aca="false">IF(OR(I10="",C10=""),"",(I10-C10)/C10)</f>
@@ -2595,9 +2891,18 @@
         <f aca="false">IF(OR(E10="",L10=""),"",IF(E10=L10,"√","×"))</f>
         <v/>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="O10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8"/>
@@ -15918,75 +16223,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.857142857142857</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.285714285714286</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.857142857142857</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.285714285714286</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.857142857142857</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -15995,33 +16300,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -16049,47 +16354,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16097,7 +16402,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16105,31 +16410,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16137,47 +16442,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="116">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -519,6 +519,21 @@
     <t xml:space="preserve">2026-09-02 06:40</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势涨转急跌(20日现货+2.9%已退出超买,10日-3.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鹰派主线未逆转(9月维持利率概率约54%+2026加息押注近半)+技术破位深化(跌破4370/4346,收于全天低位)→惯性偏空；托底:4313-4335三重支撑汇合(6月平台+50%回撤+8月突破位)+PBOC连买21月(7月+20吨近三年最大)+超买解除(20日现货口径+2.9%&lt;8%阈值)+VIX14.92无流动性冲击；连跌5日-7.3%后首测厚支撑→押跌/中档</t>
+  </si>
+  <si>
+    <t xml:space="preserve">补结算:09-03晨间定时任务未运行漏结算,今晨09-04补;实际价取北京日(06:00-06:00)收盘4386.49(lygxcjg.cn伦敦金日表,该口径与仓库历次06:30实时结算价偏差≤0.4%;另zzcha.com 09-03 04:55实时4388.33、150currency 4385.96互证);基准4329.1→4386.49=+1.33%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04 06:45</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -526,7 +541,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">趋势涨转急跌</t>
+      <t xml:space="preserve">趋势涨</t>
     </r>
     <r>
       <rPr>
@@ -545,44 +560,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日现货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已退出超买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">日</t>
     </r>
     <r>
@@ -593,7 +570,121 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-3.0%)</t>
+      <t xml:space="preserve">+7.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未超买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">型反弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日连阳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3.4%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未收复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -604,7 +695,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">鹰派主线未逆转</t>
+      <t xml:space="preserve">沃勒放鸽</t>
     </r>
     <r>
       <rPr>
@@ -614,7 +705,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(9</t>
+      <t xml:space="preserve">+ADP</t>
     </r>
     <r>
       <rPr>
@@ -623,7 +714,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月维持利率概率约</t>
+      <t xml:space="preserve">疲软→美元走弱</t>
     </r>
     <r>
       <rPr>
@@ -633,7 +724,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">54%+2026</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -642,7 +733,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">加息押注近半</t>
+      <t xml:space="preserve">昨夜</t>
     </r>
     <r>
       <rPr>
@@ -652,7 +743,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+</t>
+      <t xml:space="preserve">+2%</t>
     </r>
     <r>
       <rPr>
@@ -661,7 +752,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">技术破位深化</t>
+      <t xml:space="preserve">破</t>
     </r>
     <r>
       <rPr>
@@ -671,7 +762,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">9/1</t>
     </r>
     <r>
       <rPr>
@@ -680,7 +771,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">跌破</t>
+      <t xml:space="preserve">高点</t>
     </r>
     <r>
       <rPr>
@@ -690,7 +781,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4370/4346,</t>
+      <t xml:space="preserve">4461</t>
     </r>
     <r>
       <rPr>
@@ -699,7 +790,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">收于全天低位</t>
+      <t xml:space="preserve">冲</t>
     </r>
     <r>
       <rPr>
@@ -709,102 +800,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">惯性偏空；托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:4313-4335</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重支撑汇合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月平台</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回撤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月突破位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+PBOC</t>
+      <t xml:space="preserve">4504;PBOC</t>
     </r>
     <r>
       <rPr>
@@ -861,7 +857,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+20</t>
+      <t xml:space="preserve">+20t)+ETF</t>
     </r>
     <r>
       <rPr>
@@ -870,7 +866,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">吨近三年最大</t>
+      <t xml:space="preserve">季流入</t>
     </r>
     <r>
       <rPr>
@@ -880,7 +876,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+</t>
+      <t xml:space="preserve">222t</t>
     </r>
     <r>
       <rPr>
@@ -889,7 +885,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">超买解除</t>
+      <t xml:space="preserve">托底</t>
     </r>
     <r>
       <rPr>
@@ -899,7 +895,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(20</t>
+      <t xml:space="preserve">;</t>
     </r>
     <r>
       <rPr>
@@ -908,7 +904,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日现货口径</t>
+      <t xml:space="preserve">两连阳</t>
     </r>
     <r>
       <rPr>
@@ -918,7 +914,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+2.9%&lt;8%</t>
+      <t xml:space="preserve">+3.4%</t>
     </r>
     <r>
       <rPr>
@@ -927,7 +923,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">阈值</t>
+      <t xml:space="preserve">后今晚非农</t>
     </r>
     <r>
       <rPr>
@@ -937,7 +933,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+VIX14.92</t>
+      <t xml:space="preserve">(20:30)</t>
     </r>
     <r>
       <rPr>
@@ -946,45 +942,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">无流动性冲击；连跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后首测厚支撑→押跌</t>
+      <t xml:space="preserve">前波动收敛→押涨</t>
     </r>
     <r>
       <rPr>
@@ -1003,7 +961,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中档</t>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">风险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非农强劲引发获利兑现回踩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4461/4433</t>
     </r>
   </si>
   <si>
@@ -1014,7 +1020,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周三</t>
+      <t xml:space="preserve">周五</t>
     </r>
     <r>
       <rPr>
@@ -1024,7 +1030,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:40</t>
+      <t xml:space="preserve">06:45</t>
     </r>
     <r>
       <rPr>
@@ -1062,7 +1068,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">);</t>
     </r>
     <r>
       <rPr>
@@ -1071,7 +1077,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；方向押跌</t>
+      <t xml:space="preserve">方向押涨</t>
     </r>
     <r>
       <rPr>
@@ -1109,7 +1115,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">鹰派主线</t>
+      <t xml:space="preserve">鸽派催化</t>
     </r>
     <r>
       <rPr>
@@ -1128,7 +1134,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">破位惯性</t>
+      <t xml:space="preserve">技术突破</t>
     </r>
     <r>
       <rPr>
@@ -1147,7 +1153,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">跌速急升</t>
+      <t xml:space="preserve">结构性买盘</t>
     </r>
     <r>
       <rPr>
@@ -1157,7 +1163,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(-0.19%→-2.75%),</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -1166,64 +1172,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4313-4335</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重支撑首测</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逢低加速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超买已解除</t>
+      <t xml:space="preserve">但非农事件降档规则触发</t>
     </r>
     <r>
       <rPr>
@@ -1242,7 +1191,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">现货</t>
+      <t xml:space="preserve">原始大档→中</t>
     </r>
     <r>
       <rPr>
@@ -1252,7 +1201,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20</t>
+      <t xml:space="preserve">);9/2</t>
     </r>
     <r>
       <rPr>
@@ -1261,7 +1210,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">双错</t>
     </r>
     <r>
       <rPr>
@@ -1271,7 +1220,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+2.9%)</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1280,7 +1229,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">限制深跌</t>
+      <t xml:space="preserve">惯性看空遇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后基于当日信号独立判断</t>
     </r>
     <r>
       <rPr>
@@ -1299,121 +1286,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">小档区间几何宽度仅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.36%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">难命中→押中档；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押小被大档打脸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">累计方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2/8),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断基于当日信号独立作出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式上修</t>
+      <t xml:space="preserve">非追结果式反向修正</t>
     </r>
   </si>
   <si>
@@ -2156,7 +2029,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2855,64 +2728,82 @@
       <c r="C10" s="5" t="n">
         <v>4329.1</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="7" t="str">
+      <c r="I10" s="5" t="n">
+        <v>4386.49</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <f aca="false">IF(OR(I10="",C10=""),"",(I10-C10)/C10)</f>
-        <v/>
+        <v>0.0132567970247856</v>
       </c>
       <c r="K10" s="4" t="str">
         <f aca="false">IF(J10="","",IF(J10&gt;0,"涨",IF(J10&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L10" s="4" t="str">
         <f aca="false">IF(J10="","",IF(ABS(J10)&lt;=0.003,"小",IF(ABS(J10)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M10" s="4" t="str">
         <f aca="false">IF(OR(D10="",K10=""),"",IF(D10=K10,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N10" s="4" t="str">
         <f aca="false">IF(OR(E10="",L10=""),"",IF(E10=L10,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O10" s="12" t="s">
+        <v>×</v>
+      </c>
+      <c r="O10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="Q10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>4474</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="I11" s="9"/>
       <c r="J11" s="11" t="str">
         <f aca="false">IF(OR(I11="",C11=""),"",(I11-C11)/C11)</f>
@@ -2934,9 +2825,18 @@
         <f aca="false">IF(OR(E11="",L11=""),"",IF(E11=L11,"√","×"))</f>
         <v/>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
+      <c r="O11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="0" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -16223,75 +16123,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B3" s="15" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.875</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.25</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.875</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.25</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.875</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B10" s="15" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -16300,33 +16200,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -16354,47 +16254,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16402,7 +16302,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16410,31 +16310,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16442,47 +16342,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -534,760 +534,13 @@
     <t xml:space="preserve">2026-09-04 06:45</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+7.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未超买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">型反弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日连阳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+3.4%,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未收复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">趋势涨(20日+7.3%未超买)伴V型反弹(2日连阳+3.4%,未收复200日线)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">沃勒放鸽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ADP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">疲软→美元走弱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨夜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4461</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4504;PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20t)+ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">季流入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">222t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">两连阳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+3.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后今晚非农</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20:30)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前波动收敛→押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">风险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非农强劲引发获利兑现回踩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4461/4433</t>
-    </r>
+    <t xml:space="preserve">沃勒放鸽+ADP疲软→美元走弱,昨夜+2%破9/1高点4461冲4504;PBOC连买21月(7月+20t)+ETF季流入222t托底;两连阳+3.4%后今晚非农(20:30)前波动收敛→押涨/中;风险:非农强劲引发获利兑现回踩4461/4433</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸽派催化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术突破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结构性买盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">但非农事件降档规则触发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">原始大档→中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);9/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双错</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">惯性看空遇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后基于当日信号独立判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式反向修正</t>
-    </r>
+    <t xml:space="preserve">周五06:45晨间定时执行成功(克隆仓库版);方向押涨+档位押中:鸽派催化+技术突破+结构性买盘,但非农事件降档规则触发(原始大档→中);9/2双错(惯性看空遇V反转)后基于当日信号独立判断,非追结果式反向修正</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1980,7 +1233,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2026,10 +1279,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2789,52 +2038,54 @@
       <c r="C11" s="9" t="n">
         <v>4474</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="11" t="str">
+      <c r="I11" s="9" t="n">
+        <v>4431.1</v>
+      </c>
+      <c r="J11" s="11" t="n">
         <f aca="false">IF(OR(I11="",C11=""),"",(I11-C11)/C11)</f>
-        <v/>
+        <v>-0.0095887349128296</v>
       </c>
       <c r="K11" s="8" t="str">
         <f aca="false">IF(J11="","",IF(J11&gt;0,"涨",IF(J11&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L11" s="8" t="str">
         <f aca="false">IF(J11="","",IF(ABS(J11)&lt;=0.003,"小",IF(ABS(J11)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M11" s="8" t="str">
         <f aca="false">IF(OR(D11="",K11=""),"",IF(D11=K11,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N11" s="8" t="str">
         <f aca="false">IF(OR(E11="",L11=""),"",IF(E11=L11,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O11" s="12" t="s">
+        <v>√</v>
+      </c>
+      <c r="O11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="P11" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>60</v>
       </c>
     </row>
@@ -16122,84 +15373,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="14" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.777777777777778</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.222222222222222</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="16" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.777777777777778</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.222222222222222</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.777777777777778</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="15" t="str">
+      <c r="B10" s="14" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>81</v>
       </c>
     </row>
@@ -16218,7 +15469,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16253,87 +15504,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>104</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -541,6 +541,21 @@
   </si>
   <si>
     <t xml:space="preserve">周五06:45晨间定时执行成功(克隆仓库版);方向押涨+档位押中:鸽派催化+技术突破+结构性买盘,但非农事件降档规则触发(原始大档→中);9/2双错(惯性看空遇V反转)后基于当日信号独立判断,非追结果式反向修正</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07 06:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">趋势涨(20日+3.46%未超买)伴宽幅整理(8/24见顶4663后急跌,V型反弹4467受阻,未收复200日线4529)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非农强劲→鹰派重定价+美元近一月高位[部分定价];但周五-2%急跌尾段收复过半+PBOC连买21月(7月+20t近三年最大,总持2366t)+ETF Q2流入222t+20日+3.46%未超买+窗口内无重大事件(Fed决议在窗外)→押涨/中;风险:美元续强失守4400下探4370/4346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周一06:37晨间定时执行成功(克隆仓库版);方向押涨+档位押中:非农冲击消化+结构性买盘+未超买,Fed会前观望压窄区间但20日均幅1.16%仍高;9/4方向错后基于当日信号独立判断,非追结果式反向修正</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1062,7 +1077,7 @@
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1105,6 +1120,18 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1233,7 +1260,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1282,7 +1309,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1294,11 +1337,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1306,15 +1349,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2090,14 +2133,30 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>4429.3</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="I12" s="5"/>
       <c r="J12" s="7" t="str">
         <f aca="false">IF(OR(I12="",C12=""),"",(I12-C12)/C12)</f>
@@ -2119,9 +2178,18 @@
         <f aca="false">IF(OR(E12="",L12=""),"",IF(E12=L12,"√","×"))</f>
         <v/>
       </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="O12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" s="15" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8"/>
@@ -15373,99 +15441,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>72</v>
+      <c r="A1" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="A5" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="17" t="n">
+      <c r="A6" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="14" t="str">
+      <c r="A10" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>81</v>
+      <c r="A12" s="22" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -15474,10 +15542,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -15504,88 +15572,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>86</v>
+      <c r="A1" s="23" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>88</v>
+      <c r="A3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>90</v>
+      <c r="A4" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>92</v>
+      <c r="A5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>94</v>
+      <c r="A6" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>96</v>
+      <c r="A7" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>97</v>
+      <c r="B8" s="25" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>98</v>
+      <c r="B9" s="25" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>100</v>
+      <c r="A10" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>102</v>
+      <c r="A11" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>104</v>
+      <c r="A12" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15593,47 +15661,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="126">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -556,6 +556,616 @@
   </si>
   <si>
     <t xml:space="preserve">周一06:37晨间定时执行成功(克隆仓库版);方向押涨+档位押中:非农冲击消化+结构性买盘+未超买,Fed会前观望压窄区间但20日均幅1.16%仍高;9/4方向错后基于当日信号独立判断,非追结果式反向修正</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08 06:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3.46%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未超买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴宽幅整理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4410</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三测不破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4467</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受阻未收复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4536)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地缘避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美袭委内瑞拉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美伊紧张</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+4410</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三日不破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">但鹰派重定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元近一月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线下技术压制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹试阻力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向押涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支撑三测不破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卖压衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险增量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元高位压制反弹高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更正</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/15-16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本周三无决议</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/11</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -1260,7 +1870,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1321,7 +1931,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2157,26 +2771,28 @@
       <c r="H12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="7" t="str">
+      <c r="I12" s="5" t="n">
+        <v>4410.2</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <f aca="false">IF(OR(I12="",C12=""),"",(I12-C12)/C12)</f>
-        <v/>
+        <v>-0.00431219380037486</v>
       </c>
       <c r="K12" s="4" t="str">
         <f aca="false">IF(J12="","",IF(J12&gt;0,"涨",IF(J12&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L12" s="4" t="str">
         <f aca="false">IF(J12="","",IF(ABS(J12)&lt;=0.003,"小",IF(ABS(J12)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M12" s="4" t="str">
         <f aca="false">IF(OR(D12="",K12=""),"",IF(D12=K12,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N12" s="4" t="str">
         <f aca="false">IF(OR(E12="",L12=""),"",IF(E12=L12,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="O12" s="14" t="s">
         <v>74</v>
@@ -2192,14 +2808,30 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>4410.2</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I13" s="9"/>
       <c r="J13" s="11" t="str">
         <f aca="false">IF(OR(I13="",C13=""),"",(I13-C13)/C13)</f>
@@ -2221,9 +2853,18 @@
         <f aca="false">IF(OR(E13="",L13=""),"",IF(E13=L13,"√","×"))</f>
         <v/>
       </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
+      <c r="O13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="R13" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -15441,111 +16082,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>77</v>
+      <c r="A1" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.7</v>
+        <v>0.636363636363636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.3</v>
+        <v>0.363636363636364</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.7</v>
+        <v>0.636363636363636</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.3</v>
+        <v>0.363636363636364</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.7</v>
+        <v>0.636363636363636</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="18" t="str">
+      <c r="A10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>86</v>
+      <c r="A12" s="23" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -15572,88 +16213,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>91</v>
+      <c r="A1" s="24" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>93</v>
+      <c r="A3" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>95</v>
+      <c r="A4" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>97</v>
+      <c r="A5" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>99</v>
+      <c r="A6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>101</v>
+      <c r="A7" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>102</v>
+      <c r="B8" s="26" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>103</v>
+      <c r="B9" s="26" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>105</v>
+      <c r="A10" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>107</v>
+      <c r="A11" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>109</v>
+      <c r="A12" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15661,47 +16302,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="130">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -564,6 +564,21 @@
     <t xml:space="preserve">2026-09-08 06:35</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势涨(20日+3.46%未超买)伴宽幅整理(4410三测不破,V反4467受阻未收复200日线4536)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地缘避险(美袭委内瑞拉+美伊紧张)+4410三日不破+央行购金21连月托底[部分定价];但鹰派重定价+美元近一月高位+200日线下技术压制,反弹试阻力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周二06:35晨间定时执行成功(克隆仓库版);方向押涨+档位押中:支撑三测不破+卖压衰竭+避险增量,美元高位压制反弹高度;更正:FOMC实为9/15-16本周三无决议,CPI周五9/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09 06:41</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -571,7 +586,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">趋势涨</t>
+      <t xml:space="preserve">震荡</t>
     </r>
     <r>
       <rPr>
@@ -600,7 +615,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+3.46%</t>
+      <t xml:space="preserve">+1.55%,60</t>
     </r>
     <r>
       <rPr>
@@ -609,7 +624,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未超买</t>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.09%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4663</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落后重返区间起点</t>
     </r>
     <r>
       <rPr>
@@ -628,7 +681,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">伴宽幅整理</t>
+      <t xml:space="preserve">伴短期下行加速</t>
     </r>
     <r>
       <rPr>
@@ -638,7 +691,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(4410</t>
+      <t xml:space="preserve">(10</t>
     </r>
     <r>
       <rPr>
@@ -647,7 +700,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三测不破</t>
+      <t xml:space="preserve">日</t>
     </r>
     <r>
       <rPr>
@@ -657,7 +710,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">,V</t>
+      <t xml:space="preserve">-5.60%</t>
     </r>
     <r>
       <rPr>
@@ -666,7 +719,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">反</t>
+      <t xml:space="preserve">三连阴破</t>
     </r>
     <r>
       <rPr>
@@ -676,7 +729,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4467</t>
+      <t xml:space="preserve">4400,</t>
     </r>
     <r>
       <rPr>
@@ -685,7 +738,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">受阻未收复</t>
+      <t xml:space="preserve">逼近百日线</t>
     </r>
     <r>
       <rPr>
@@ -695,7 +748,19 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">200</t>
+      <t xml:space="preserve">4346)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4410</t>
     </r>
     <r>
       <rPr>
@@ -704,7 +769,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日线</t>
+      <t xml:space="preserve">三测支撑</t>
     </r>
     <r>
       <rPr>
@@ -714,10 +779,8 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4536)</t>
+      <t xml:space="preserve">9/8</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -725,7 +788,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">地缘避险</t>
+      <t xml:space="preserve">破位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.23%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4400/4380)+FedWatch 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息概率约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元强势</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术阻力最小路径向下</t>
     </r>
     <r>
       <rPr>
@@ -744,7 +883,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美袭委内瑞拉</t>
+      <t xml:space="preserve">百日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4346</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为下一关口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4300)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价回吐</t>
     </r>
     <r>
       <rPr>
@@ -763,7 +959,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美伊紧张</t>
+      <t xml:space="preserve">投机持仓撤离；支撑</t>
     </r>
     <r>
       <rPr>
@@ -773,7 +969,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)+4410</t>
+      <t xml:space="preserve">:PBOC</t>
     </r>
     <r>
       <rPr>
@@ -782,7 +978,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三日不破</t>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逢低接货</t>
     </r>
     <r>
       <rPr>
@@ -801,7 +1054,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">央行购金</t>
+      <t xml:space="preserve">百日线首触争夺</t>
     </r>
     <r>
       <rPr>
@@ -811,7 +1064,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">21</t>
+      <t xml:space="preserve">+10</t>
     </r>
     <r>
       <rPr>
@@ -820,7 +1073,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连月托底</t>
+      <t xml:space="preserve">日</t>
     </r>
     <r>
       <rPr>
@@ -830,7 +1083,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[</t>
+      <t xml:space="preserve">-5.6%</t>
     </r>
     <r>
       <rPr>
@@ -839,170 +1092,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">但鹰派重定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元近一月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线下技术压制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反弹试阻力</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
+      <t xml:space="preserve">超卖反弹弹性；风险</t>
     </r>
     <r>
       <rPr>
@@ -1021,7 +1111,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">支撑三测不破</t>
+      <t xml:space="preserve">超跌反弹</t>
     </r>
     <r>
       <rPr>
@@ -1031,7 +1121,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1040,131 +1130,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">卖压衰竭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险增量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元高位压制反弹高度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">更正</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/15-16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本周三无决议</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/11</t>
+      <t xml:space="preserve">地缘再升级</t>
     </r>
   </si>
   <si>
@@ -1935,7 +1901,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2817,64 +2783,82 @@
       <c r="C13" s="9" t="n">
         <v>4410.2</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="11" t="str">
+      <c r="I13" s="9" t="n">
+        <v>4356</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <f aca="false">IF(OR(I13="",C13=""),"",(I13-C13)/C13)</f>
-        <v/>
+        <v>-0.0122896920774568</v>
       </c>
       <c r="K13" s="8" t="str">
         <f aca="false">IF(J13="","",IF(J13&gt;0,"涨",IF(J13&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L13" s="8" t="str">
         <f aca="false">IF(J13="","",IF(ABS(J13)&lt;=0.003,"小",IF(ABS(J13)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M13" s="8" t="str">
         <f aca="false">IF(OR(D13="",K13=""),"",IF(D13=K13,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N13" s="8" t="str">
         <f aca="false">IF(OR(E13="",L13=""),"",IF(E13=L13,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O13" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O13" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="P13" s="16" t="s">
+      <c r="P13" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="Q13" s="16" t="s">
+      <c r="Q13" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4356.7</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="7" t="str">
         <f aca="false">IF(OR(I14="",C14=""),"",(I14-C14)/C14)</f>
@@ -2896,9 +2880,16 @@
         <f aca="false">IF(OR(E14="",L14=""),"",IF(E14=L14,"√","×"))</f>
         <v/>
       </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
+      <c r="O14" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="Q14" s="4"/>
+      <c r="R14" s="0" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8"/>
@@ -16083,75 +16074,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.636363636363636</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.363636363636364</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.636363636363636</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.363636363636364</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.636363636363636</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -16160,33 +16151,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -16214,47 +16205,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16262,7 +16253,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16270,31 +16261,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16302,47 +16293,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="135">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -579,177 +579,7 @@
     <t xml:space="preserve">2026-09-09 06:41</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.55%,60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.09%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4663</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回落后重返区间起点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴短期下行加速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-5.60%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三连阴破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4400,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逼近百日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4346)</t>
-    </r>
+    <t xml:space="preserve">震荡(20日+1.55%,60日+1.09%自4663回落后重返区间起点)伴短期下行加速(10日-5.60%三连阴破4400,逼近百日线4346)</t>
   </si>
   <si>
     <r>
@@ -1131,6 +961,892 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">地缘再升级</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10 06:46</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">震荡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.73%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴超卖反弹启动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/9+1.08%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4400,10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4.9%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4329→4356</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">抬高高点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4474→4409</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下移收敛三角</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4410</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原三测支撑变阻力昨夜首触回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4408.9→4403.7)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派主线未逆转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息概率约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元近一月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+PPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗口内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">明晚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下周三连事件前夜波动收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.08%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短线获利盘落袋倾向；托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:RSI30.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖修复刚启动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4346</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">首触获承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低点抬高；押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高位窄幅整理微跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非赌深跌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续四日方向错</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/9)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后本判断基于当日信号独立作出——昨夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4410</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力首触回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三连事件前夜收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派主线未变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同时超卖修复与央行买盘限制深跌→押反弹衰竭微跌整理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式反向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未翻多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；累计方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7/13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4/13</t>
     </r>
   </si>
   <si>
@@ -1901,7 +2617,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2844,62 +3560,80 @@
       <c r="C14" s="5" t="n">
         <v>4356.7</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="7" t="str">
+      <c r="I14" s="5" t="n">
+        <v>4403.7</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <f aca="false">IF(OR(I14="",C14=""),"",(I14-C14)/C14)</f>
-        <v/>
+        <v>0.0107879817292905</v>
       </c>
       <c r="K14" s="4" t="str">
         <f aca="false">IF(J14="","",IF(J14&gt;0,"涨",IF(J14&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L14" s="4" t="str">
         <f aca="false">IF(J14="","",IF(ABS(J14)&lt;=0.003,"小",IF(ABS(J14)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M14" s="4" t="str">
         <f aca="false">IF(OR(D14="",K14=""),"",IF(D14=K14,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N14" s="4" t="str">
         <f aca="false">IF(OR(E14="",L14=""),"",IF(E14=L14,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O14" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O14" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>85</v>
       </c>
       <c r="Q14" s="4"/>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>4403.7</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I15" s="9"/>
       <c r="J15" s="11" t="str">
         <f aca="false">IF(OR(I15="",C15=""),"",(I15-C15)/C15)</f>
@@ -2921,9 +3655,18 @@
         <f aca="false">IF(OR(E15="",L15=""),"",IF(E15=L15,"√","×"))</f>
         <v/>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
+      <c r="O15" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="R15" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -16074,66 +16817,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.583333333333333</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.583333333333333</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
@@ -16142,7 +16885,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -16151,33 +16894,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -16205,47 +16948,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16253,7 +16996,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16261,31 +17004,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16293,47 +17036,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="140">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -970,158 +970,7 @@
     <t xml:space="preserve">2026-09-10 06:46</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.73%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴超卖反弹启动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/9+1.08%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4400,10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-4.9%,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4329→4356</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">抬高高点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4474→4409</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下移收敛三角</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">震荡(20日+1.73%)伴超卖反弹启动(9/9+1.08%收复4400,10日约-4.9%,低点4329→4356抬高高点4474→4409下移收敛三角)</t>
   </si>
   <si>
     <r>
@@ -1506,6 +1355,15 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">周四06:46晨间定时执行成功(克隆仓库版)；方向押跌+档位押小:连续四日方向错(9/4、9/7、9/8、9/9)后本判断基于当日信号独立作出——昨夜4410阻力首触回落+三连事件前夜收敛+鹰派主线未变,同时超卖修复与央行买盘限制深跌→押反弹衰竭微跌整理,非追结果式反向(未翻多)；累计方向7/13、档位4/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11 06:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1513,7 +1371,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周四</t>
+      <t xml:space="preserve">震荡</t>
     </r>
     <r>
       <rPr>
@@ -1523,7 +1381,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:46</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -1532,6 +1390,570 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.72%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴破位下行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失守百日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4346/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月低点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4329,10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">距</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.46%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术三重破位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4346+9/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4329+60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日区间下沿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收于低位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派主线未逆转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息概率约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元近一月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30 CPI(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月预期偏热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">落在窗口正中；托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:RSI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖加深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近三年最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+4300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整数关口买盘；事件降档规则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始大档→中</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">晨间定时执行成功</t>
     </r>
     <r>
@@ -1589,7 +2011,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位押小</t>
+      <t xml:space="preserve">档位押中</t>
     </r>
     <r>
       <rPr>
@@ -1608,7 +2030,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连续四日方向错</t>
+      <t xml:space="preserve">破位惯性</t>
     </r>
     <r>
       <rPr>
@@ -1618,7 +2040,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(9/4</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -1627,7 +2049,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、</t>
+      <t xml:space="preserve">鹰派主线</t>
     </r>
     <r>
       <rPr>
@@ -1637,7 +2059,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/7</t>
+      <t xml:space="preserve">+CPI</t>
     </r>
     <r>
       <rPr>
@@ -1646,7 +2068,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、</t>
+      <t xml:space="preserve">落地兑现</t>
     </r>
     <r>
       <rPr>
@@ -1656,7 +2078,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/8</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -1665,7 +2087,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、</t>
+      <t xml:space="preserve">事件降档规则原始大→中</t>
     </r>
     <r>
       <rPr>
@@ -1675,7 +2097,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/9)</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1684,7 +2106,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">后本判断基于当日信号独立作出——昨夜</t>
+      <t xml:space="preserve">非追结果式上修</t>
     </r>
     <r>
       <rPr>
@@ -1694,7 +2116,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4410</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -1703,7 +2125,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">阻力首触回落</t>
+      <t xml:space="preserve">基于当日信号独立判断</t>
     </r>
     <r>
       <rPr>
@@ -1713,6 +2135,101 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日均幅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.04%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日实际档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">+</t>
     </r>
     <r>
@@ -1722,7 +2239,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三连事件前夜收敛</t>
+      <t xml:space="preserve">破位首日</t>
     </r>
     <r>
       <rPr>
@@ -1732,7 +2249,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+</t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -1741,7 +2258,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">鹰派主线未变</t>
+      <t xml:space="preserve">；规则冻结期沿用既有规则；</t>
     </r>
     <r>
       <rPr>
@@ -1751,7 +2268,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">,</t>
+      <t xml:space="preserve">9/10</t>
     </r>
     <r>
       <rPr>
@@ -1760,7 +2277,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">同时超卖修复与央行买盘限制深跌→押反弹衰竭微跌整理</t>
+      <t xml:space="preserve">方向√档位</t>
     </r>
     <r>
       <rPr>
@@ -1770,7 +2287,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">,</t>
+      <t xml:space="preserve">×</t>
     </r>
     <r>
       <rPr>
@@ -1779,7 +2296,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非追结果式反向</t>
+      <t xml:space="preserve">后累计方向</t>
     </r>
     <r>
       <rPr>
@@ -1789,7 +2306,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">8/14</t>
     </r>
     <r>
       <rPr>
@@ -1798,7 +2315,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未翻多</t>
+      <t xml:space="preserve">、档位</t>
     </r>
     <r>
       <rPr>
@@ -1808,45 +2325,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；累计方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7/13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/13</t>
+      <t xml:space="preserve">4/14</t>
     </r>
   </si>
   <si>
@@ -2617,7 +3096,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3619,64 +4098,82 @@
       <c r="C15" s="9" t="n">
         <v>4403.7</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="11" t="str">
+      <c r="I15" s="9" t="n">
+        <v>4319.9</v>
+      </c>
+      <c r="J15" s="11" t="n">
         <f aca="false">IF(OR(I15="",C15=""),"",(I15-C15)/C15)</f>
-        <v/>
+        <v>-0.0190294525058474</v>
       </c>
       <c r="K15" s="8" t="str">
         <f aca="false">IF(J15="","",IF(J15&gt;0,"涨",IF(J15&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L15" s="8" t="str">
         <f aca="false">IF(J15="","",IF(ABS(J15)&lt;=0.003,"小",IF(ABS(J15)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M15" s="8" t="str">
         <f aca="false">IF(OR(D15="",K15=""),"",IF(D15=K15,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N15" s="8" t="str">
         <f aca="false">IF(OR(E15="",L15=""),"",IF(E15=L15,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O15" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O15" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="Q15" s="16" t="s">
+      <c r="Q15" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="R15" s="0" t="n">
+      <c r="R15" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4319.9</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="7" t="str">
         <f aca="false">IF(OR(I16="",C16=""),"",(I16-C16)/C16)</f>
@@ -3698,9 +4195,18 @@
         <f aca="false">IF(OR(E16="",L16=""),"",IF(E16=L16,"√","×"))</f>
         <v/>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="O16" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="R16" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8"/>
@@ -16817,66 +17323,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.538461538461538</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.307692307692308</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.538461538461538</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.307692307692308</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
@@ -16885,7 +17391,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -16894,33 +17400,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -16948,47 +17454,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16996,7 +17502,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17004,31 +17510,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17036,47 +17542,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -1364,969 +1364,13 @@
     <t xml:space="preserve">2026-09-11 06:35</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.72%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴破位下行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨夜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">失守百日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4346/9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月低点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4329,10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6%,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">距</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.46%)</t>
-    </r>
+    <t xml:space="preserve">震荡(20日+0.72%)伴破位下行(昨夜-1.9%失守百日线4346/9月低点4329,10日约-6%,距4300关口-0.46%)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术三重破位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4346+9/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4329+60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日区间下沿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨夜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收于低位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派主线未逆转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息概率约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元近一月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30 CPI(8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月预期偏热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">落在窗口正中；托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:RSI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖加深</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近三年最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+4300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">整数关口买盘；事件降档规则</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">原始大档→中</t>
-    </r>
+    <t xml:space="preserve">技术三重破位(百日线4346+9/1低点4329+60日区间下沿)昨夜PPI后-1.9%收于低位+鹰派主线未逆转(9月加息概率约60%美元近一月高位)+今晚20:30 CPI(8月预期偏热)落在窗口正中；托底:RSI约30超卖加深+PBOC连买21月(7月+20t近三年最大)+4300整数关口买盘；事件降档规则:原始大档→中</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；方向押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位惯性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派主线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">落地兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事件降档规则原始大→中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式上修</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基于当日信号独立判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日均幅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.04%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日实际档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位首日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；规则冻结期沿用既有规则；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向√档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后累计方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8/14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/14</t>
-    </r>
+    <t xml:space="preserve">周五06:35晨间定时执行成功(克隆仓库版)；方向押跌+档位押中:破位惯性+鹰派主线+CPI落地兑现,事件降档规则原始大→中(非追结果式上修,基于当日信号独立判断:20日均幅1.04%+近5日实际档位3大2中+破位首日)；规则冻结期沿用既有规则；9/10方向√档位×后累计方向8/14、档位4/14</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -3031,7 +2075,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3093,10 +2137,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4159,52 +3199,54 @@
       <c r="C16" s="5" t="n">
         <v>4319.9</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="7" t="str">
+      <c r="I16" s="5" t="n">
+        <v>4349.7</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <f aca="false">IF(OR(I16="",C16=""),"",(I16-C16)/C16)</f>
-        <v/>
+        <v>0.00689830783119984</v>
       </c>
       <c r="K16" s="4" t="str">
         <f aca="false">IF(J16="","",IF(J16&gt;0,"涨",IF(J16&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L16" s="4" t="str">
         <f aca="false">IF(J16="","",IF(ABS(J16)&lt;=0.003,"小",IF(ABS(J16)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M16" s="4" t="str">
         <f aca="false">IF(OR(D16="",K16=""),"",IF(D16=K16,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N16" s="4" t="str">
         <f aca="false">IF(OR(E16="",L16=""),"",IF(E16=L16,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O16" s="16" t="s">
+        <v>√</v>
+      </c>
+      <c r="O16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="16" t="s">
+      <c r="P16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Q16" s="16" t="s">
+      <c r="Q16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="R16" s="0" t="n">
+      <c r="R16" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -17322,84 +16364,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.571428571428571</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.285714285714286</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.571428571428571</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.285714285714286</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>105</v>
       </c>
     </row>
@@ -17418,7 +16460,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17453,87 +16495,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>128</v>
       </c>
     </row>
